--- a/evaluation/gpt_realset.xlsx
+++ b/evaluation/gpt_realset.xlsx
@@ -349,7 +349,7 @@
         <v>0.7947180346357484</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.9388888888888889</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.21510598783406007</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.18095238095238095</v>
+        <v>0.5576893052302888</v>
       </c>
     </row>
     <row r="3">
@@ -399,7 +399,7 @@
         <v>0.24537029653405526</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.2236111111111111</v>
+        <v>0.5436237373737374</v>
       </c>
     </row>
     <row r="5">
@@ -415,7 +415,7 @@
         <v>0.26683794723123094</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.12654320987654322</v>
+        <v>0.49508978675645343</v>
       </c>
     </row>
     <row r="6">
@@ -463,8 +463,10 @@
       <c r="B8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>0.571003612434054</v>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
@@ -501,8 +503,10 @@
       <c r="B10" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="0" t="n">
-        <v>0.06666666666666667</v>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
@@ -523,7 +527,7 @@
         <v>0.7875138353197244</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.6616541353383458</v>
       </c>
     </row>
     <row r="12">
@@ -539,7 +543,7 @@
         <v>0.7131889022778672</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -555,7 +559,7 @@
         <v>0.13233398208773048</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.12251984126984128</v>
+        <v>0.5612599206349207</v>
       </c>
     </row>
     <row r="14">
@@ -571,7 +575,7 @@
         <v>0.0</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.0</v>
+        <v>0.38235294117647056</v>
       </c>
     </row>
     <row r="15">
@@ -587,7 +591,7 @@
         <v>0.22370190829846018</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.06108452950558213</v>
+        <v>0.39467269953539974</v>
       </c>
     </row>
     <row r="16">
@@ -603,7 +607,7 @@
         <v>0.07490026121050584</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.37629937629937626</v>
       </c>
     </row>
     <row r="17">
@@ -619,7 +623,7 @@
         <v>0.41394173053393263</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.32613636363636367</v>
+        <v>0.5191287878787879</v>
       </c>
     </row>
     <row r="18">
@@ -635,7 +639,7 @@
         <v>0.13071917044165374</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.03121527777777778</v>
+        <v>0.40022302350427347</v>
       </c>
     </row>
     <row r="19">
@@ -683,7 +687,7 @@
         <v>0.2113778663963243</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.375</v>
+        <v>0.5056818181818181</v>
       </c>
     </row>
     <row r="22">
@@ -699,7 +703,7 @@
         <v>0.21713622875752067</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.5841269841269842</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/gpt_realset.xlsx
+++ b/evaluation/gpt_realset.xlsx
@@ -333,7 +333,7 @@
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.7947180346357484</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.9388888888888889</v>
+        <v>0.8777777777777778</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.21510598783406007</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.5576893052302888</v>
+        <v>0.16908665105386417</v>
       </c>
     </row>
     <row r="3">
@@ -399,7 +399,7 @@
         <v>0.24537029653405526</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.5436237373737374</v>
+        <v>0.19311868686868686</v>
       </c>
     </row>
     <row r="5">
@@ -415,7 +415,7 @@
         <v>0.26683794723123094</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.49508978675645343</v>
+        <v>0.10928731762065096</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         <v>0.7875138353197244</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.6616541353383458</v>
+        <v>0.3834586466165414</v>
       </c>
     </row>
     <row r="12">
@@ -543,7 +543,7 @@
         <v>0.7131889022778672</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -559,7 +559,7 @@
         <v>0.13233398208773048</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.5612599206349207</v>
+        <v>0.12251984126984128</v>
       </c>
     </row>
     <row r="14">
@@ -575,7 +575,7 @@
         <v>0.0</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.38235294117647056</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -591,7 +591,7 @@
         <v>0.22370190829846018</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.39467269953539974</v>
+        <v>0.044485472574717425</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>0.07490026121050584</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.37629937629937626</v>
+        <v>0.05197505197505198</v>
       </c>
     </row>
     <row r="17">
@@ -623,7 +623,7 @@
         <v>0.41394173053393263</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.5191287878787879</v>
+        <v>0.23224862258953172</v>
       </c>
     </row>
     <row r="18">
@@ -639,7 +639,7 @@
         <v>0.13071917044165374</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.40022302350427347</v>
+        <v>0.024011752136752135</v>
       </c>
     </row>
     <row r="19">
@@ -687,7 +687,7 @@
         <v>0.2113778663963243</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.5056818181818181</v>
+        <v>0.23863636363636365</v>
       </c>
     </row>
     <row r="22">
@@ -703,7 +703,7 @@
         <v>0.21713622875752067</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.5841269841269842</v>
+        <v>0.26666666666666666</v>
       </c>
     </row>
   </sheetData>
